--- a/salida.xlsx
+++ b/salida.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/62582315a8a39068/Trabajo IM/APP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_9D1A42597AE3B6673321D4C9D5B2BAE84DDE4BCA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EA6C227-12AE-4DBE-9BB6-1F894EF3506C}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_95DEF3875F2A8FE430B40D2F5EF00BE94DD9B403" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE9303CF-B762-42C9-8417-8312AA58EFFB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4412" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4480" uniqueCount="39">
   <si>
     <t>Fecha</t>
   </si>
@@ -200,9 +200,1121 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-UY"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Resumen_semanal!$L$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Visitados_prom_dia</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Resumen_semanal!$A$2:$A$38</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="37"/>
+                <c:pt idx="0">
+                  <c:v>45719</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45726</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>45733</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45740</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45747</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45754</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45761</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45768</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45775</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45782</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45789</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>45796</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>45803</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>45810</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>45817</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>45824</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>45831</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>45838</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>45845</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>45852</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>45859</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>45866</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>45873</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>45880</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>45887</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>45894</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>45901</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>45908</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>45915</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>45922</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>45929</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>45936</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>45943</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>45950</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>45957</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>45964</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>45971</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Resumen_semanal!$L$2:$L$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="37"/>
+                <c:pt idx="0">
+                  <c:v>3504.8571428571399</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4026.5714285714298</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4119.4285714285697</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3690.1428571428601</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3899</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4175.4285714285697</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4345.4285714285697</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4023.4285714285702</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3153.8571428571399</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3960.5714285714298</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4062</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4530.2857142857101</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4007.8571428571399</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4145.7142857142899</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4327</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4221.5714285714303</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4129.2857142857101</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3949.2857142857101</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4106</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4051.4285714285702</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4781.2857142857101</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4342.1428571428596</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4649.5714285714303</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3965.1428571428601</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4744.4285714285697</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>4723.5714285714303</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>4954.4285714285697</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>4520.2857142857101</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>4815</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>4764.8571428571404</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3904.1428571428601</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>4228.8571428571404</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3332</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>3741.5714285714298</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2812.7142857142899</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>3507.8571428571399</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>3090.7142857142899</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FDC6-4AA0-B5FD-62C95C6B5C7A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1456865888"/>
+        <c:axId val="1456869728"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1456865888"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="m/d/yyyy" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-UY"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1456869728"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1456869728"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-UY"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1456865888"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-UY"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>685800</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>161930</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>171449</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{526372D7-0199-6994-10B4-081EA9EF1D1D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tabla_db" displayName="tabla_db" ref="A1:I2041" totalsRowShown="0">
-  <autoFilter ref="A1:I2041" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tabla_db" displayName="tabla_db" ref="A1:I2073" totalsRowShown="0">
+  <autoFilter ref="A1:I2073" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fecha"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Dia"/>
@@ -219,8 +1331,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="tabla_pordia" displayName="tabla_pordia" ref="A1:H256" totalsRowShown="0">
-  <autoFilter ref="A1:H256" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="tabla_pordia" displayName="tabla_pordia" ref="A1:H260" totalsRowShown="0">
+  <autoFilter ref="A1:H260" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Fecha"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Dia"/>
@@ -555,10 +1667,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I2041"/>
+  <dimension ref="A1:I2073"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.7109375" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" customWidth="1"/>
     <col min="3" max="3" width="9.7109375" customWidth="1"/>
     <col min="4" max="4" width="12.7109375" customWidth="1"/>
@@ -59758,6 +60870,934 @@
         <v>22</v>
       </c>
     </row>
+    <row r="2042" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2042" s="1">
+        <v>45974</v>
+      </c>
+      <c r="B2042" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2042" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2042">
+        <v>708</v>
+      </c>
+      <c r="E2042">
+        <v>477</v>
+      </c>
+      <c r="F2042">
+        <v>347</v>
+      </c>
+      <c r="G2042">
+        <v>130</v>
+      </c>
+      <c r="H2042">
+        <v>317</v>
+      </c>
+      <c r="I2042">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2043" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2043" s="1">
+        <v>45974</v>
+      </c>
+      <c r="B2043" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2043" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2043">
+        <v>252</v>
+      </c>
+      <c r="E2043">
+        <v>144</v>
+      </c>
+      <c r="F2043">
+        <v>78</v>
+      </c>
+      <c r="G2043">
+        <v>66</v>
+      </c>
+      <c r="H2043">
+        <v>77</v>
+      </c>
+      <c r="I2043">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2044" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2044" s="1">
+        <v>45974</v>
+      </c>
+      <c r="B2044" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2044" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2044">
+        <v>951</v>
+      </c>
+      <c r="E2044">
+        <v>888</v>
+      </c>
+      <c r="F2044">
+        <v>724</v>
+      </c>
+      <c r="G2044">
+        <v>164</v>
+      </c>
+      <c r="H2044">
+        <v>715</v>
+      </c>
+      <c r="I2044">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2045" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2045" s="1">
+        <v>45974</v>
+      </c>
+      <c r="B2045" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2045" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2045">
+        <v>952</v>
+      </c>
+      <c r="E2045">
+        <v>806</v>
+      </c>
+      <c r="F2045">
+        <v>806</v>
+      </c>
+      <c r="G2045">
+        <v>0</v>
+      </c>
+      <c r="H2045">
+        <v>795</v>
+      </c>
+      <c r="I2045">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2046" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2046" s="1">
+        <v>45974</v>
+      </c>
+      <c r="B2046" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2046" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2046">
+        <v>1039</v>
+      </c>
+      <c r="E2046">
+        <v>629</v>
+      </c>
+      <c r="F2046">
+        <v>472</v>
+      </c>
+      <c r="G2046">
+        <v>157</v>
+      </c>
+      <c r="H2046">
+        <v>420</v>
+      </c>
+      <c r="I2046">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2047" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2047" s="1">
+        <v>45974</v>
+      </c>
+      <c r="B2047" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2047" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2047">
+        <v>513</v>
+      </c>
+      <c r="E2047">
+        <v>917</v>
+      </c>
+      <c r="F2047">
+        <v>615</v>
+      </c>
+      <c r="G2047">
+        <v>302</v>
+      </c>
+      <c r="H2047">
+        <v>586</v>
+      </c>
+      <c r="I2047">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2048" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2048" s="1">
+        <v>45974</v>
+      </c>
+      <c r="B2048" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2048" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2048">
+        <v>292</v>
+      </c>
+      <c r="E2048">
+        <v>631</v>
+      </c>
+      <c r="F2048">
+        <v>546</v>
+      </c>
+      <c r="G2048">
+        <v>85</v>
+      </c>
+      <c r="H2048">
+        <v>479</v>
+      </c>
+      <c r="I2048">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2049" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2049" s="1">
+        <v>45974</v>
+      </c>
+      <c r="B2049" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2049" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2049">
+        <v>740</v>
+      </c>
+      <c r="E2049">
+        <v>666</v>
+      </c>
+      <c r="F2049">
+        <v>439</v>
+      </c>
+      <c r="G2049">
+        <v>227</v>
+      </c>
+      <c r="H2049">
+        <v>394</v>
+      </c>
+      <c r="I2049">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2050" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2050" s="1">
+        <v>45975</v>
+      </c>
+      <c r="B2050" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2050" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2050">
+        <v>699</v>
+      </c>
+      <c r="E2050">
+        <v>824</v>
+      </c>
+      <c r="F2050">
+        <v>398</v>
+      </c>
+      <c r="G2050">
+        <v>426</v>
+      </c>
+      <c r="H2050">
+        <v>352</v>
+      </c>
+      <c r="I2050">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2051" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2051" s="1">
+        <v>45975</v>
+      </c>
+      <c r="B2051" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2051" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2051">
+        <v>47</v>
+      </c>
+      <c r="E2051">
+        <v>201</v>
+      </c>
+      <c r="F2051">
+        <v>155</v>
+      </c>
+      <c r="G2051">
+        <v>46</v>
+      </c>
+      <c r="H2051">
+        <v>153</v>
+      </c>
+      <c r="I2051">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2052" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2052" s="1">
+        <v>45975</v>
+      </c>
+      <c r="B2052" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2052" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2052">
+        <v>701</v>
+      </c>
+      <c r="E2052">
+        <v>631</v>
+      </c>
+      <c r="F2052">
+        <v>503</v>
+      </c>
+      <c r="G2052">
+        <v>128</v>
+      </c>
+      <c r="H2052">
+        <v>494</v>
+      </c>
+      <c r="I2052">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2053" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2053" s="1">
+        <v>45975</v>
+      </c>
+      <c r="B2053" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2053" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2053">
+        <v>832</v>
+      </c>
+      <c r="E2053">
+        <v>807</v>
+      </c>
+      <c r="F2053">
+        <v>801</v>
+      </c>
+      <c r="G2053">
+        <v>6</v>
+      </c>
+      <c r="H2053">
+        <v>781</v>
+      </c>
+      <c r="I2053">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2054" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2054" s="1">
+        <v>45975</v>
+      </c>
+      <c r="B2054" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2054" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2054">
+        <v>353</v>
+      </c>
+      <c r="E2054">
+        <v>812</v>
+      </c>
+      <c r="F2054">
+        <v>589</v>
+      </c>
+      <c r="G2054">
+        <v>223</v>
+      </c>
+      <c r="H2054">
+        <v>502</v>
+      </c>
+      <c r="I2054">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2055" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2055" s="1">
+        <v>45975</v>
+      </c>
+      <c r="B2055" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2055" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2055">
+        <v>900</v>
+      </c>
+      <c r="E2055">
+        <v>695</v>
+      </c>
+      <c r="F2055">
+        <v>342</v>
+      </c>
+      <c r="G2055">
+        <v>353</v>
+      </c>
+      <c r="H2055">
+        <v>331</v>
+      </c>
+      <c r="I2055">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2056" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2056" s="1">
+        <v>45975</v>
+      </c>
+      <c r="B2056" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2056" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2056">
+        <v>1099</v>
+      </c>
+      <c r="E2056">
+        <v>543</v>
+      </c>
+      <c r="F2056">
+        <v>359</v>
+      </c>
+      <c r="G2056">
+        <v>184</v>
+      </c>
+      <c r="H2056">
+        <v>313</v>
+      </c>
+      <c r="I2056">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2057" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2057" s="1">
+        <v>45975</v>
+      </c>
+      <c r="B2057" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2057" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2057">
+        <v>667</v>
+      </c>
+      <c r="E2057">
+        <v>597</v>
+      </c>
+      <c r="F2057">
+        <v>276</v>
+      </c>
+      <c r="G2057">
+        <v>321</v>
+      </c>
+      <c r="H2057">
+        <v>258</v>
+      </c>
+      <c r="I2057">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2058" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2058" s="1">
+        <v>45976</v>
+      </c>
+      <c r="B2058" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2058" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2058">
+        <v>708</v>
+      </c>
+      <c r="E2058">
+        <v>882</v>
+      </c>
+      <c r="F2058">
+        <v>523</v>
+      </c>
+      <c r="G2058">
+        <v>359</v>
+      </c>
+      <c r="H2058">
+        <v>446</v>
+      </c>
+      <c r="I2058">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2059" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2059" s="1">
+        <v>45976</v>
+      </c>
+      <c r="B2059" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2059" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2059">
+        <v>0</v>
+      </c>
+      <c r="E2059">
+        <v>0</v>
+      </c>
+      <c r="F2059">
+        <v>0</v>
+      </c>
+      <c r="G2059">
+        <v>0</v>
+      </c>
+      <c r="H2059">
+        <v>0</v>
+      </c>
+      <c r="I2059">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2060" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2060" s="1">
+        <v>45976</v>
+      </c>
+      <c r="B2060" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2060" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2060">
+        <v>0</v>
+      </c>
+      <c r="E2060">
+        <v>66</v>
+      </c>
+      <c r="F2060">
+        <v>7</v>
+      </c>
+      <c r="G2060">
+        <v>59</v>
+      </c>
+      <c r="H2060">
+        <v>6</v>
+      </c>
+      <c r="I2060">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2061" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2061" s="1">
+        <v>45976</v>
+      </c>
+      <c r="B2061" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2061" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2061">
+        <v>0</v>
+      </c>
+      <c r="E2061">
+        <v>7</v>
+      </c>
+      <c r="F2061">
+        <v>3</v>
+      </c>
+      <c r="G2061">
+        <v>4</v>
+      </c>
+      <c r="H2061">
+        <v>2</v>
+      </c>
+      <c r="I2061">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2062" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2062" s="1">
+        <v>45976</v>
+      </c>
+      <c r="B2062" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2062" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2062">
+        <v>938</v>
+      </c>
+      <c r="E2062">
+        <v>292</v>
+      </c>
+      <c r="F2062">
+        <v>200</v>
+      </c>
+      <c r="G2062">
+        <v>92</v>
+      </c>
+      <c r="H2062">
+        <v>167</v>
+      </c>
+      <c r="I2062">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2063" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2063" s="1">
+        <v>45976</v>
+      </c>
+      <c r="B2063" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2063" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2063">
+        <v>291</v>
+      </c>
+      <c r="E2063">
+        <v>136</v>
+      </c>
+      <c r="F2063">
+        <v>83</v>
+      </c>
+      <c r="G2063">
+        <v>53</v>
+      </c>
+      <c r="H2063">
+        <v>74</v>
+      </c>
+      <c r="I2063">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2064" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2064" s="1">
+        <v>45976</v>
+      </c>
+      <c r="B2064" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2064" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2064">
+        <v>292</v>
+      </c>
+      <c r="E2064">
+        <v>701</v>
+      </c>
+      <c r="F2064">
+        <v>363</v>
+      </c>
+      <c r="G2064">
+        <v>338</v>
+      </c>
+      <c r="H2064">
+        <v>313</v>
+      </c>
+      <c r="I2064">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2065" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2065" s="1">
+        <v>45976</v>
+      </c>
+      <c r="B2065" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2065" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2065">
+        <v>740</v>
+      </c>
+      <c r="E2065">
+        <v>507</v>
+      </c>
+      <c r="F2065">
+        <v>286</v>
+      </c>
+      <c r="G2065">
+        <v>221</v>
+      </c>
+      <c r="H2065">
+        <v>263</v>
+      </c>
+      <c r="I2065">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2066" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2066" s="1">
+        <v>45977</v>
+      </c>
+      <c r="B2066" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2066" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2066">
+        <v>140</v>
+      </c>
+      <c r="E2066">
+        <v>0</v>
+      </c>
+      <c r="F2066">
+        <v>0</v>
+      </c>
+      <c r="G2066">
+        <v>0</v>
+      </c>
+      <c r="H2066">
+        <v>0</v>
+      </c>
+      <c r="I2066">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2067" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2067" s="1">
+        <v>45977</v>
+      </c>
+      <c r="B2067" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2067" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2067">
+        <v>299</v>
+      </c>
+      <c r="E2067">
+        <v>163</v>
+      </c>
+      <c r="F2067">
+        <v>105</v>
+      </c>
+      <c r="G2067">
+        <v>58</v>
+      </c>
+      <c r="H2067">
+        <v>102</v>
+      </c>
+      <c r="I2067">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2068" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2068" s="1">
+        <v>45977</v>
+      </c>
+      <c r="B2068" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2068" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2068">
+        <v>951</v>
+      </c>
+      <c r="E2068">
+        <v>685</v>
+      </c>
+      <c r="F2068">
+        <v>452</v>
+      </c>
+      <c r="G2068">
+        <v>233</v>
+      </c>
+      <c r="H2068">
+        <v>439</v>
+      </c>
+      <c r="I2068">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2069" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2069" s="1">
+        <v>45977</v>
+      </c>
+      <c r="B2069" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2069" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2069">
+        <v>1784</v>
+      </c>
+      <c r="E2069">
+        <v>992</v>
+      </c>
+      <c r="F2069">
+        <v>859</v>
+      </c>
+      <c r="G2069">
+        <v>133</v>
+      </c>
+      <c r="H2069">
+        <v>845</v>
+      </c>
+      <c r="I2069">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2070" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2070" s="1">
+        <v>45977</v>
+      </c>
+      <c r="B2070" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2070" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2070">
+        <v>453</v>
+      </c>
+      <c r="E2070">
+        <v>100</v>
+      </c>
+      <c r="F2070">
+        <v>50</v>
+      </c>
+      <c r="G2070">
+        <v>50</v>
+      </c>
+      <c r="H2070">
+        <v>48</v>
+      </c>
+      <c r="I2070">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2071" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2071" s="1">
+        <v>45977</v>
+      </c>
+      <c r="B2071" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2071" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2071">
+        <v>446</v>
+      </c>
+      <c r="E2071">
+        <v>317</v>
+      </c>
+      <c r="F2071">
+        <v>225</v>
+      </c>
+      <c r="G2071">
+        <v>92</v>
+      </c>
+      <c r="H2071">
+        <v>222</v>
+      </c>
+      <c r="I2071">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2072" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2072" s="1">
+        <v>45977</v>
+      </c>
+      <c r="B2072" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2072" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2072">
+        <v>0</v>
+      </c>
+      <c r="E2072">
+        <v>2</v>
+      </c>
+      <c r="F2072">
+        <v>2</v>
+      </c>
+      <c r="G2072">
+        <v>0</v>
+      </c>
+      <c r="H2072">
+        <v>1</v>
+      </c>
+      <c r="I2072">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2073" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2073" s="1">
+        <v>45977</v>
+      </c>
+      <c r="B2073" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2073" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2073">
+        <v>0</v>
+      </c>
+      <c r="E2073">
+        <v>223</v>
+      </c>
+      <c r="F2073">
+        <v>124</v>
+      </c>
+      <c r="G2073">
+        <v>99</v>
+      </c>
+      <c r="H2073">
+        <v>113</v>
+      </c>
+      <c r="I2073">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -59769,10 +61809,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H256"/>
+  <dimension ref="A1:H260"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="10.7109375" customWidth="1"/>
@@ -66436,6 +68476,110 @@
       </c>
       <c r="H256">
         <v>255</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A257" s="1">
+        <v>45974</v>
+      </c>
+      <c r="B257" t="s">
+        <v>20</v>
+      </c>
+      <c r="C257">
+        <v>5447</v>
+      </c>
+      <c r="D257">
+        <v>5158</v>
+      </c>
+      <c r="E257">
+        <v>4027</v>
+      </c>
+      <c r="F257">
+        <v>1131</v>
+      </c>
+      <c r="G257">
+        <v>3783</v>
+      </c>
+      <c r="H257">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A258" s="1">
+        <v>45975</v>
+      </c>
+      <c r="B258" t="s">
+        <v>21</v>
+      </c>
+      <c r="C258">
+        <v>5298</v>
+      </c>
+      <c r="D258">
+        <v>5110</v>
+      </c>
+      <c r="E258">
+        <v>3423</v>
+      </c>
+      <c r="F258">
+        <v>1687</v>
+      </c>
+      <c r="G258">
+        <v>3184</v>
+      </c>
+      <c r="H258">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A259" s="1">
+        <v>45976</v>
+      </c>
+      <c r="B259" t="s">
+        <v>22</v>
+      </c>
+      <c r="C259">
+        <v>2969</v>
+      </c>
+      <c r="D259">
+        <v>2591</v>
+      </c>
+      <c r="E259">
+        <v>1465</v>
+      </c>
+      <c r="F259">
+        <v>1126</v>
+      </c>
+      <c r="G259">
+        <v>1271</v>
+      </c>
+      <c r="H259">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A260" s="1">
+        <v>45977</v>
+      </c>
+      <c r="B260" t="s">
+        <v>23</v>
+      </c>
+      <c r="C260">
+        <v>4073</v>
+      </c>
+      <c r="D260">
+        <v>2482</v>
+      </c>
+      <c r="E260">
+        <v>1817</v>
+      </c>
+      <c r="F260">
+        <v>665</v>
+      </c>
+      <c r="G260">
+        <v>1770</v>
+      </c>
+      <c r="H260">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -69224,53 +71368,54 @@
         <v>45971</v>
       </c>
       <c r="B38" s="1">
-        <v>45973</v>
+        <v>45977</v>
       </c>
       <c r="C38">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D38">
-        <v>16032</v>
+        <v>33819</v>
       </c>
       <c r="E38">
-        <v>16355</v>
+        <v>31696</v>
       </c>
       <c r="F38">
-        <v>10903</v>
+        <v>21635</v>
       </c>
       <c r="G38">
-        <v>5452</v>
+        <v>10061</v>
       </c>
       <c r="H38">
-        <v>10196</v>
+        <v>20204</v>
       </c>
       <c r="I38">
-        <v>707</v>
+        <v>1431</v>
       </c>
       <c r="J38">
-        <v>5344</v>
+        <v>4831.2857142857101</v>
       </c>
       <c r="K38">
-        <v>5451.6666666666697</v>
+        <v>4528</v>
       </c>
       <c r="L38">
-        <v>3634.3333333333298</v>
+        <v>3090.7142857142899</v>
       </c>
       <c r="M38">
-        <v>1817.3333333333301</v>
+        <v>1437.2857142857099</v>
       </c>
       <c r="N38">
-        <v>3398.6666666666702</v>
+        <v>2886.2857142857101</v>
       </c>
       <c r="O38">
-        <v>235.666666666667</v>
+        <v>204.42857142857099</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/salida.xlsx
+++ b/salida.xlsx
@@ -185,8 +185,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tabla_db" displayName="tabla_db" ref="A1:I2601" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:I2601"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tabla_db" displayName="tabla_db" ref="A1:I2609" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:I2609"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Dia"/>
@@ -203,8 +203,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tabla_pordia" displayName="tabla_pordia" ref="A1:H326" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:H326"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tabla_pordia" displayName="tabla_pordia" ref="A1:H327" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:H327"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Dia"/>
@@ -75982,6 +75982,238 @@
         <v>73</v>
       </c>
     </row>
+    <row r="2602">
+      <c r="A2602" s="1" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B2602" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2602" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2602" t="n">
+        <v>701</v>
+      </c>
+      <c r="E2602" t="n">
+        <v>778</v>
+      </c>
+      <c r="F2602" t="n">
+        <v>564</v>
+      </c>
+      <c r="G2602" t="n">
+        <v>214</v>
+      </c>
+      <c r="H2602" t="n">
+        <v>462</v>
+      </c>
+      <c r="I2602" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2603">
+      <c r="A2603" s="1" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B2603" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2603" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2603" t="n">
+        <v>248</v>
+      </c>
+      <c r="E2603" t="n">
+        <v>144</v>
+      </c>
+      <c r="F2603" t="n">
+        <v>143</v>
+      </c>
+      <c r="G2603" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2603" t="n">
+        <v>138</v>
+      </c>
+      <c r="I2603" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2604">
+      <c r="A2604" s="1" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B2604" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2604" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2604" t="n">
+        <v>953</v>
+      </c>
+      <c r="E2604" t="n">
+        <v>979</v>
+      </c>
+      <c r="F2604" t="n">
+        <v>817</v>
+      </c>
+      <c r="G2604" t="n">
+        <v>162</v>
+      </c>
+      <c r="H2604" t="n">
+        <v>797</v>
+      </c>
+      <c r="I2604" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2605">
+      <c r="A2605" s="1" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B2605" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2605" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2605" t="n">
+        <v>952</v>
+      </c>
+      <c r="E2605" t="n">
+        <v>894</v>
+      </c>
+      <c r="F2605" t="n">
+        <v>894</v>
+      </c>
+      <c r="G2605" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2605" t="n">
+        <v>869</v>
+      </c>
+      <c r="I2605" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2606">
+      <c r="A2606" s="1" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B2606" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2606" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2606" t="n">
+        <v>1031</v>
+      </c>
+      <c r="E2606" t="n">
+        <v>878</v>
+      </c>
+      <c r="F2606" t="n">
+        <v>646</v>
+      </c>
+      <c r="G2606" t="n">
+        <v>232</v>
+      </c>
+      <c r="H2606" t="n">
+        <v>544</v>
+      </c>
+      <c r="I2606" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2607">
+      <c r="A2607" s="1" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B2607" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2607" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2607" t="n">
+        <v>481</v>
+      </c>
+      <c r="E2607" t="n">
+        <v>908</v>
+      </c>
+      <c r="F2607" t="n">
+        <v>665</v>
+      </c>
+      <c r="G2607" t="n">
+        <v>243</v>
+      </c>
+      <c r="H2607" t="n">
+        <v>624</v>
+      </c>
+      <c r="I2607" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2608">
+      <c r="A2608" s="1" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B2608" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2608" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2608" t="n">
+        <v>285</v>
+      </c>
+      <c r="E2608" t="n">
+        <v>742</v>
+      </c>
+      <c r="F2608" t="n">
+        <v>348</v>
+      </c>
+      <c r="G2608" t="n">
+        <v>394</v>
+      </c>
+      <c r="H2608" t="n">
+        <v>308</v>
+      </c>
+      <c r="I2608" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2609">
+      <c r="A2609" s="1" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B2609" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2609" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2609" t="n">
+        <v>731</v>
+      </c>
+      <c r="E2609" t="n">
+        <v>805</v>
+      </c>
+      <c r="F2609" t="n">
+        <v>504</v>
+      </c>
+      <c r="G2609" t="n">
+        <v>301</v>
+      </c>
+      <c r="H2609" t="n">
+        <v>465</v>
+      </c>
+      <c r="I2609" t="n">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -84480,6 +84712,32 @@
       </c>
       <c r="H326" t="n">
         <v>326</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B327" t="s">
+        <v>20</v>
+      </c>
+      <c r="C327" t="n">
+        <v>5382</v>
+      </c>
+      <c r="D327" t="n">
+        <v>6128</v>
+      </c>
+      <c r="E327" t="n">
+        <v>4581</v>
+      </c>
+      <c r="F327" t="n">
+        <v>1547</v>
+      </c>
+      <c r="G327" t="n">
+        <v>4207</v>
+      </c>
+      <c r="H327" t="n">
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -87999,46 +88257,46 @@
         <v>46041</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>15731</v>
+        <v>21113</v>
       </c>
       <c r="E48" t="n">
-        <v>17777</v>
+        <v>23905</v>
       </c>
       <c r="F48" t="n">
-        <v>12020</v>
+        <v>16601</v>
       </c>
       <c r="G48" t="n">
-        <v>5757</v>
+        <v>7304</v>
       </c>
       <c r="H48" t="n">
-        <v>11173</v>
+        <v>15380</v>
       </c>
       <c r="I48" t="n">
-        <v>847</v>
+        <v>1221</v>
       </c>
       <c r="J48" t="n">
-        <v>5243.66666666667</v>
+        <v>5278.25</v>
       </c>
       <c r="K48" t="n">
-        <v>5925.66666666667</v>
+        <v>5976.25</v>
       </c>
       <c r="L48" t="n">
-        <v>4006.66666666667</v>
+        <v>4150.25</v>
       </c>
       <c r="M48" t="n">
-        <v>1919</v>
+        <v>1826</v>
       </c>
       <c r="N48" t="n">
-        <v>3724.33333333333</v>
+        <v>3845</v>
       </c>
       <c r="O48" t="n">
-        <v>282.333333333333</v>
+        <v>305.25</v>
       </c>
     </row>
   </sheetData>
